--- a/AAII_Financials/Quarterly/NABL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NABL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="92">
   <si>
     <t>NABL</t>
   </si>
@@ -656,390 +656,403 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>133700</v>
+        <v>138200</v>
       </c>
       <c r="E8" s="3">
+        <v>132400</v>
+      </c>
+      <c r="F8" s="3">
         <v>130300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>131700</v>
       </c>
-      <c r="G8" s="3">
-        <v>131200</v>
-      </c>
       <c r="H8" s="3">
+        <v>130500</v>
+      </c>
+      <c r="I8" s="3">
         <v>118200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>116500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>116400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>119400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>113700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>108400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>107600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>106100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>99800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>95800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>93500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>91600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>90900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>89500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>88400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>85300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>83200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>79900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>76300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>73400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>73300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>69500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>67200</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>27500</v>
+        <v>27800</v>
       </c>
       <c r="E9" s="3">
+        <v>27600</v>
+      </c>
+      <c r="F9" s="3">
         <v>26800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>25400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>24500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>23500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>21200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>19400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>18700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>17800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>17200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>16900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>16600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>15800</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>15100</v>
       </c>
       <c r="R9" s="3">
         <v>15100</v>
       </c>
       <c r="S9" s="3">
+        <v>15100</v>
+      </c>
+      <c r="T9" s="3">
         <v>14200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>14300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>13300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>12300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>12800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>14000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>16800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>16000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>15400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>15000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>14600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>14100</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>106200</v>
+        <v>110400</v>
       </c>
       <c r="E10" s="3">
+        <v>104800</v>
+      </c>
+      <c r="F10" s="3">
         <v>103500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>106300</v>
       </c>
-      <c r="G10" s="3">
-        <v>106800</v>
-      </c>
       <c r="H10" s="3">
+        <v>106000</v>
+      </c>
+      <c r="I10" s="3">
         <v>94700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>95300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>97000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>100700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>95900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>91300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>90700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>89500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>84100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>80700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>78400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>77400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>76600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>76200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>76100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>72500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>69200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>63200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>60300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>58000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>58300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>54900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>53100</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1070,94 +1083,98 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>26600</v>
+      </c>
+      <c r="E12" s="3">
         <v>26100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>25300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>25200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>26300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>23900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>23200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>23000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>22400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>22100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>19400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>19800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>20200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>18200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>16800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>16000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>15200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>15400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>14800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>14600</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>12500</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>12000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>10800</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>10400</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>10100</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>11400</v>
-      </c>
-      <c r="AC12" s="3">
-        <v>9700</v>
       </c>
       <c r="AD12" s="3">
         <v>9700</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3">
+        <v>9700</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1242,53 +1259,56 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E14" s="3">
         <v>700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-15200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>5500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>6000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>6100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-5100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-4200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>5200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-1400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1400</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
@@ -1328,8 +1348,11 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1349,10 +1372,10 @@
         <v>4700</v>
       </c>
       <c r="I15" s="3">
+        <v>4700</v>
+      </c>
+      <c r="J15" s="3">
         <v>2400</v>
-      </c>
-      <c r="J15" s="3">
-        <v>500</v>
       </c>
       <c r="K15" s="3">
         <v>500</v>
@@ -1370,10 +1393,10 @@
         <v>500</v>
       </c>
       <c r="P15" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q15" s="3">
         <v>1000</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>1500</v>
       </c>
       <c r="R15" s="3">
         <v>1500</v>
@@ -1388,34 +1411,37 @@
         <v>1500</v>
       </c>
       <c r="V15" s="3">
+        <v>1500</v>
+      </c>
+      <c r="W15" s="3">
         <v>1600</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>4300</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>6000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>6100</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>6000</v>
-      </c>
-      <c r="AA15" s="3">
-        <v>5900</v>
       </c>
       <c r="AB15" s="3">
         <v>5900</v>
       </c>
       <c r="AC15" s="3">
+        <v>5900</v>
+      </c>
+      <c r="AD15" s="3">
         <v>5800</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1443,180 +1469,187 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>120500</v>
+        <v>120000</v>
       </c>
       <c r="E17" s="3">
+        <v>120600</v>
+      </c>
+      <c r="F17" s="3">
         <v>132200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>114600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>115200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>110300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>105700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>96700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>92300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>94000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>88100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>89700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>90100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>84100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>81400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>81800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>81300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>79800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>81000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>78700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>75500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>78000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>79400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>67100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>59900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>62700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>57400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>57100</v>
       </c>
     </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>13200</v>
+        <v>18200</v>
       </c>
       <c r="E18" s="3">
+        <v>11800</v>
+      </c>
+      <c r="F18" s="3">
         <v>-2000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>17100</v>
       </c>
-      <c r="G18" s="3">
-        <v>16100</v>
-      </c>
       <c r="H18" s="3">
+        <v>15300</v>
+      </c>
+      <c r="I18" s="3">
         <v>7900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>10800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>19700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>27200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>19700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>20400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>17900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>16000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>15700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>14400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>11700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>10300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>11100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>8500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>9700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>9800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>5200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>9200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>13500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>10600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>12100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>10100</v>
       </c>
     </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1647,438 +1680,454 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>400</v>
+      </c>
+      <c r="E20" s="3">
         <v>700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>3700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-4800</v>
       </c>
-      <c r="G20" s="3">
-        <v>900</v>
-      </c>
       <c r="H20" s="3">
+        <v>800</v>
+      </c>
+      <c r="I20" s="3">
         <v>-1400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-2300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-2700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>400</v>
-      </c>
-      <c r="O20" s="3">
-        <v>-1000</v>
       </c>
       <c r="P20" s="3">
         <v>-1000</v>
       </c>
       <c r="Q20" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="R20" s="3">
         <v>2400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-900</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-500</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>-7000</v>
       </c>
       <c r="Z20" s="3">
         <v>-7000</v>
       </c>
       <c r="AA20" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="AB20" s="3">
         <v>100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-8000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-8400</v>
       </c>
     </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>17200</v>
+        <v>22500</v>
       </c>
       <c r="E21" s="3">
+        <v>15800</v>
+      </c>
+      <c r="F21" s="3">
         <v>-1000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>26700</v>
       </c>
-      <c r="G21" s="3">
-        <v>20000</v>
-      </c>
       <c r="H21" s="3">
+        <v>19200</v>
+      </c>
+      <c r="I21" s="3">
         <v>14000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>11500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>22400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>28800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>20500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>23500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>18000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>17400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>17700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>22900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>16000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>16400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>18500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>17400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>14700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>17800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>16000</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AA21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB21" s="3">
         <v>41100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>23800</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E22" s="3">
         <v>7600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>12200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>8600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>8100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>7100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>7300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>7500</v>
-      </c>
-      <c r="K22" s="3">
-        <v>7600</v>
       </c>
       <c r="L22" s="3">
         <v>7600</v>
       </c>
       <c r="M22" s="3">
+        <v>7600</v>
+      </c>
+      <c r="N22" s="3">
         <v>7700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>7800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>7500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>7200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>6400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>5100</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>3800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>3500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>4800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>3100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>6100</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>6500</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AA22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB22" s="3">
         <v>7100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>7600</v>
       </c>
-      <c r="AC22" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD22" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E23" s="3">
+        <v>2800</v>
+      </c>
+      <c r="F23" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="G23" s="3">
+        <v>7800</v>
+      </c>
+      <c r="H23" s="3">
+        <v>400</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="J23" s="3">
+        <v>7000</v>
+      </c>
+      <c r="K23" s="3">
+        <v>18600</v>
+      </c>
+      <c r="L23" s="3">
+        <v>15500</v>
+      </c>
+      <c r="M23" s="3">
+        <v>13200</v>
+      </c>
+      <c r="N23" s="3">
+        <v>16800</v>
+      </c>
+      <c r="O23" s="3">
+        <v>10100</v>
+      </c>
+      <c r="P23" s="3">
+        <v>9300</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>8100</v>
+      </c>
+      <c r="R23" s="3">
+        <v>10400</v>
+      </c>
+      <c r="S23" s="3">
+        <v>4800</v>
+      </c>
+      <c r="T23" s="3">
+        <v>6600</v>
+      </c>
+      <c r="U23" s="3">
+        <v>8600</v>
+      </c>
+      <c r="V23" s="3">
+        <v>3900</v>
+      </c>
+      <c r="W23" s="3">
+        <v>5800</v>
+      </c>
+      <c r="X23" s="3">
+        <v>3700</v>
+      </c>
+      <c r="Y23" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="Z23" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="AA23" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AB23" s="3">
+        <v>6500</v>
+      </c>
+      <c r="AC23" s="3">
+        <v>2700</v>
+      </c>
+      <c r="AD23" s="3">
         <v>4200</v>
       </c>
-      <c r="E23" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="F23" s="3">
-        <v>7800</v>
-      </c>
-      <c r="G23" s="3">
-        <v>1200</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-3900</v>
-      </c>
-      <c r="I23" s="3">
-        <v>7000</v>
-      </c>
-      <c r="J23" s="3">
-        <v>18600</v>
-      </c>
-      <c r="K23" s="3">
-        <v>15500</v>
-      </c>
-      <c r="L23" s="3">
-        <v>13200</v>
-      </c>
-      <c r="M23" s="3">
-        <v>16800</v>
-      </c>
-      <c r="N23" s="3">
-        <v>10100</v>
-      </c>
-      <c r="O23" s="3">
-        <v>9300</v>
-      </c>
-      <c r="P23" s="3">
-        <v>8100</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>10400</v>
-      </c>
-      <c r="R23" s="3">
-        <v>4800</v>
-      </c>
-      <c r="S23" s="3">
-        <v>6600</v>
-      </c>
-      <c r="T23" s="3">
-        <v>8600</v>
-      </c>
-      <c r="U23" s="3">
-        <v>3900</v>
-      </c>
-      <c r="V23" s="3">
-        <v>5800</v>
-      </c>
-      <c r="W23" s="3">
-        <v>3700</v>
-      </c>
-      <c r="X23" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="Y23" s="3">
-        <v>-6500</v>
-      </c>
-      <c r="Z23" s="3">
-        <v>2100</v>
-      </c>
-      <c r="AA23" s="3">
-        <v>6500</v>
-      </c>
-      <c r="AB23" s="3">
-        <v>2700</v>
-      </c>
-      <c r="AC23" s="3">
-        <v>4200</v>
-      </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>4800</v>
+        <v>6000</v>
       </c>
       <c r="E24" s="3">
         <v>4500</v>
       </c>
       <c r="F24" s="3">
+        <v>4500</v>
+      </c>
+      <c r="G24" s="3">
         <v>6400</v>
       </c>
-      <c r="G24" s="3">
-        <v>5200</v>
-      </c>
       <c r="H24" s="3">
+        <v>5000</v>
+      </c>
+      <c r="I24" s="3">
         <v>3300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>3700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>7900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>6100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>5700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>7400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>4100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>4800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>4600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>3400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>4500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>3500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>3900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>3300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>2400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>3500</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>3300</v>
       </c>
       <c r="AA24" s="3">
         <v>3300</v>
       </c>
       <c r="AB24" s="3">
+        <v>3300</v>
+      </c>
+      <c r="AC24" s="3">
         <v>2000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>2300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2163,180 +2212,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-600</v>
+        <v>1800</v>
       </c>
       <c r="E26" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F26" s="3">
         <v>-7200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1400</v>
       </c>
-      <c r="G26" s="3">
-        <v>-4000</v>
-      </c>
       <c r="H26" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="I26" s="3">
         <v>-7200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>10800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>9500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>7500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>9400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>6000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>3500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>7000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>4300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>5100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-4300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-9900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>3200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-600</v>
+        <v>1800</v>
       </c>
       <c r="E27" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F27" s="3">
         <v>-7200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1400</v>
       </c>
-      <c r="G27" s="3">
-        <v>-4000</v>
-      </c>
       <c r="H27" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="I27" s="3">
         <v>-7200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>10800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>9500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>7500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>9400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>6000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>3500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>7000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>4300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>5100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-4300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-9900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>3200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2421,8 +2479,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2507,8 +2568,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2593,8 +2657,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2679,180 +2746,189 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-3700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>4800</v>
       </c>
-      <c r="G32" s="3">
-        <v>-900</v>
-      </c>
       <c r="H32" s="3">
+        <v>-800</v>
+      </c>
+      <c r="I32" s="3">
         <v>1400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>2300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>2700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-400</v>
-      </c>
-      <c r="O32" s="3">
-        <v>1000</v>
       </c>
       <c r="P32" s="3">
         <v>1000</v>
       </c>
       <c r="Q32" s="3">
+        <v>1000</v>
+      </c>
+      <c r="R32" s="3">
         <v>-2400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>900</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>500</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>7000</v>
       </c>
       <c r="Z32" s="3">
         <v>7000</v>
       </c>
       <c r="AA32" s="3">
+        <v>7000</v>
+      </c>
+      <c r="AB32" s="3">
         <v>-100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>8000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>8400</v>
       </c>
     </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-600</v>
+        <v>1800</v>
       </c>
       <c r="E33" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F33" s="3">
         <v>-7200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1400</v>
       </c>
-      <c r="G33" s="3">
-        <v>-4000</v>
-      </c>
       <c r="H33" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="I33" s="3">
         <v>-7200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>3300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>10800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>9500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>7500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>9400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>6000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>3500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>7000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>4300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>5100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-4300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-9900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>3200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2937,185 +3013,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-600</v>
+        <v>1800</v>
       </c>
       <c r="E35" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F35" s="3">
         <v>-7200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1400</v>
       </c>
-      <c r="G35" s="3">
-        <v>-4000</v>
-      </c>
       <c r="H35" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="I35" s="3">
         <v>-7200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>3300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>10800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>9500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>7500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>9400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>6000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>3500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>7000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>4300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>5100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-4300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-9900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>3200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3146,8 +3231,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3178,77 +3264,78 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>115800</v>
+      </c>
+      <c r="E41" s="3">
         <v>117800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>111800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>101400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>93900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>94100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>85200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>174400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>157500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>139200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>153000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>127400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>109200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>98100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>98800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>87700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>86600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>70400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>66700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>61600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>49600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>111200</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z41" s="3" t="s">
         <v>16</v>
       </c>
@@ -3264,8 +3351,11 @@
       <c r="AD41" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3350,77 +3440,80 @@
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>72300</v>
+      </c>
+      <c r="E43" s="3">
         <v>69600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>83100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>79100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>75100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>70100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>85400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>92500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>68400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>50200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>61300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>55800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>55900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>49600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>42600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>41600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>43200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>42200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>40300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>38600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>31700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>30800</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z43" s="3" t="s">
         <v>16</v>
       </c>
@@ -3436,8 +3529,11 @@
       <c r="AD43" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3480,8 +3576,8 @@
       <c r="P44" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -3522,32 +3618,35 @@
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E45" s="3">
         <v>3000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2000</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J45" s="3">
         <v>1700</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>16</v>
       </c>
@@ -3566,33 +3665,33 @@
       <c r="P45" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R45" s="3">
         <v>12700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>14300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>13600</v>
-      </c>
-      <c r="T45" s="3">
-        <v>14000</v>
       </c>
       <c r="U45" s="3">
         <v>14000</v>
       </c>
       <c r="V45" s="3">
+        <v>14000</v>
+      </c>
+      <c r="W45" s="3">
         <v>13600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>9500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>8500</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z45" s="3" t="s">
         <v>16</v>
       </c>
@@ -3608,77 +3707,80 @@
       <c r="AD45" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>211800</v>
+      </c>
+      <c r="E46" s="3">
         <v>211000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>216400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>200300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>186700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>183800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>183900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>282300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>252200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>222300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>224800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>203900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>183600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>162600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>154200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>143600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>143400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>126600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>121000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>113800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>90800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>150600</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z46" s="3" t="s">
         <v>16</v>
       </c>
@@ -3694,8 +3796,11 @@
       <c r="AD46" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3738,8 +3843,8 @@
       <c r="P47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -3780,77 +3885,80 @@
       <c r="AD47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>80100</v>
+      </c>
+      <c r="E48" s="3">
         <v>72900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>66600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>68900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>68100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>65300</v>
-      </c>
-      <c r="I48" s="3">
-        <v>64200</v>
       </c>
       <c r="J48" s="3">
         <v>64200</v>
       </c>
       <c r="K48" s="3">
+        <v>64200</v>
+      </c>
+      <c r="L48" s="3">
         <v>64100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>66100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>68900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>66400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>67900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>67600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>69200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>70300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>70900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>73400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>75000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>75700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>61400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>32700</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z48" s="3" t="s">
         <v>16</v>
       </c>
@@ -3866,77 +3974,80 @@
       <c r="AD48" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1067400</v>
+      </c>
+      <c r="E49" s="3">
         <v>1074700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1113300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1093800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1097500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1070000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1079000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>849300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>832600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>835900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>863500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>828800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>839200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>841000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>837700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>805900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>813300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>839100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>849000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>861000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>873700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>874000</v>
       </c>
-      <c r="Y49" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z49" s="3" t="s">
         <v>16</v>
       </c>
@@ -3952,8 +4063,11 @@
       <c r="AD49" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4038,8 +4152,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4124,77 +4241,80 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>29800</v>
+      </c>
+      <c r="E52" s="3">
         <v>29300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>27700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>25900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>30900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>26600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>24800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>24600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>22000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>20800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>19800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>17900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>11600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>11200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>11100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>10800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>12100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>12900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>10800</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z52" s="3" t="s">
         <v>16</v>
       </c>
@@ -4210,8 +4330,11 @@
       <c r="AD52" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4296,77 +4419,80 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1395500</v>
+      </c>
+      <c r="E54" s="3">
         <v>1395300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1409900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1398100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1386000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1352100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1338800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1223500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1174700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1149900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1162800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1122700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1113000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1092600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1078900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1031500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1038800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1050200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1055700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1062600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1038800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1068100</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z54" s="3" t="s">
         <v>16</v>
       </c>
@@ -4382,8 +4508,11 @@
       <c r="AD54" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4414,8 +4543,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4446,77 +4576,78 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>17700</v>
+      </c>
+      <c r="E57" s="3">
         <v>13700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>9000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>8000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>7600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>6300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>6500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>6200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>5900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>5500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2200</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z57" s="3" t="s">
         <v>16</v>
       </c>
@@ -4532,77 +4663,80 @@
       <c r="AD57" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E58" s="3">
         <v>10400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>11200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>10500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>10400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>10200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>9500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>9600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>9400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>9800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>9900</v>
-      </c>
-      <c r="N58" s="3">
-        <v>9300</v>
       </c>
       <c r="O58" s="3">
         <v>9300</v>
       </c>
       <c r="P58" s="3">
+        <v>9300</v>
+      </c>
+      <c r="Q58" s="3">
         <v>9200</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>3500</v>
       </c>
       <c r="R58" s="3">
         <v>3500</v>
       </c>
       <c r="S58" s="3">
+        <v>3500</v>
+      </c>
+      <c r="T58" s="3">
         <v>3600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>3500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>4000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>3500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>20400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>19100</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z58" s="3" t="s">
         <v>16</v>
       </c>
@@ -4618,77 +4752,80 @@
       <c r="AD58" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>90600</v>
+      </c>
+      <c r="E59" s="3">
         <v>103100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>106000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>90000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>88300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>93900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>84500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>31200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>24400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>24500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>19000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>25600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>21700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>21900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>54800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>53100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>50500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>49400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>51000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>49000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>37100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>40100</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z59" s="3" t="s">
         <v>16</v>
       </c>
@@ -4704,77 +4841,80 @@
       <c r="AD59" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>162400</v>
+      </c>
+      <c r="E60" s="3">
         <v>167400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>181800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>158400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>151100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>153700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>150100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>93800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>85000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>73800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>81700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>79600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>73600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>63900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>61800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>59400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>58500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>56100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>60900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>58000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>57700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>61400</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z60" s="3" t="s">
         <v>16</v>
       </c>
@@ -4790,77 +4930,80 @@
       <c r="AD60" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>425200</v>
+      </c>
+      <c r="E61" s="3">
         <v>425300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>419200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>358500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>360900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>359900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>359700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>362300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>360800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>362600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>364600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>362900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>363100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>364800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>333500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>334000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>334400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>334900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>335400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>335800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>304000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>372700</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
       <c r="Z61" s="3">
         <v>0</v>
       </c>
@@ -4876,77 +5019,80 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="E62" s="3">
         <v>700</v>
       </c>
       <c r="F62" s="3">
+        <v>700</v>
+      </c>
+      <c r="G62" s="3">
         <v>59900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>58200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>56400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>63300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>5200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>5500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>41500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>43900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>39900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>40600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>41100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>50900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>43800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>19300</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z62" s="3" t="s">
         <v>16</v>
       </c>
@@ -4962,8 +5108,11 @@
       <c r="AD62" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5048,8 +5197,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5134,8 +5286,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5220,77 +5375,80 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>590900</v>
+      </c>
+      <c r="E66" s="3">
         <v>596500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>605300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>584700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>576600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>577000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>579600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>458500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>450300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>440900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>451400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>448000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>444100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>436400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>436800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>437300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>432800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>431600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>437300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>444700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>405500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>453400</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z66" s="3" t="s">
         <v>16</v>
       </c>
@@ -5306,8 +5464,11 @@
       <c r="AD66" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5338,8 +5499,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5424,8 +5586,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5510,8 +5675,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5596,8 +5764,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5682,68 +5853,71 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>52800</v>
+      </c>
+      <c r="E72" s="3">
         <v>53600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>54200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>61400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>60000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>64000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>71200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>67900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>57200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>47700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>40200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>30900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>24900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>20400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>16800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>9800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>9600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>5200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>100</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W72" s="3" t="s">
         <v>16</v>
       </c>
@@ -5759,8 +5933,8 @@
       <c r="AA72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AB72" s="3">
-        <v>0</v>
+      <c r="AB72" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AC72" s="3">
         <v>0</v>
@@ -5768,8 +5942,11 @@
       <c r="AD72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5854,8 +6031,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5940,8 +6120,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6026,77 +6209,80 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>804600</v>
+      </c>
+      <c r="E76" s="3">
         <v>798800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>804700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>813400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>809400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>775100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>759300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>765000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>724400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>709100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>711400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>674700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>668900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>656200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>642100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>594100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>606000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>618600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>618400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>617900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>633300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>614700</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z76" s="3" t="s">
         <v>16</v>
       </c>
@@ -6112,8 +6298,11 @@
       <c r="AD76" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6198,185 +6387,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-600</v>
+        <v>1800</v>
       </c>
       <c r="E81" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F81" s="3">
         <v>-7200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1400</v>
       </c>
-      <c r="G81" s="3">
-        <v>-4000</v>
-      </c>
       <c r="H81" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="I81" s="3">
         <v>-7200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>3300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>10800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>9500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>7500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>9400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>6000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>3500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>7000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>4300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>5100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-4300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-9900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>3200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6407,19 +6605,20 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E83" s="3">
         <v>4200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>500</v>
-      </c>
-      <c r="F83" s="3">
-        <v>4000</v>
       </c>
       <c r="G83" s="3">
         <v>4000</v>
@@ -6428,56 +6627,56 @@
         <v>4000</v>
       </c>
       <c r="I83" s="3">
+        <v>4000</v>
+      </c>
+      <c r="J83" s="3">
         <v>1600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>4600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>3200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>3300</v>
-      </c>
-      <c r="O83" s="3">
-        <v>3200</v>
       </c>
       <c r="P83" s="3">
         <v>3200</v>
       </c>
       <c r="Q83" s="3">
+        <v>3200</v>
+      </c>
+      <c r="R83" s="3">
         <v>6200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>6000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>5900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>6300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>8700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>5800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>8000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>11300</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z83" s="3" t="s">
         <v>16</v>
       </c>
@@ -6493,8 +6692,11 @@
       <c r="AD83" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6579,8 +6781,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6665,8 +6870,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6751,8 +6959,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6837,8 +7048,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6923,77 +7137,80 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>26500</v>
+      </c>
+      <c r="E89" s="3">
         <v>17500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>25300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>24000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>24200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>19700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>26000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>22000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>27300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>4200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>31200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>27500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>20700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>10600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>18400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>17100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>22700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>13100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>19200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>3100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>9900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>13200</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>16</v>
       </c>
@@ -7009,8 +7226,11 @@
       <c r="AD89" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE89" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7041,77 +7261,78 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-6600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-7200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-3100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4300</v>
-      </c>
-      <c r="S91" s="3">
-        <v>-2700</v>
       </c>
       <c r="T91" s="3">
         <v>-2700</v>
       </c>
       <c r="U91" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="V91" s="3">
         <v>-11300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-6700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-10300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z91" s="3" t="s">
         <v>16</v>
       </c>
@@ -7127,8 +7348,11 @@
       <c r="AD91" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7213,8 +7437,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7299,77 +7526,80 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-12500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-7000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-9400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-6500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-6100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-106800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-5300</v>
-      </c>
-      <c r="K94" s="3">
-        <v>-5100</v>
       </c>
       <c r="L94" s="3">
         <v>-5100</v>
       </c>
       <c r="M94" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="N94" s="3">
         <v>-5200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-5500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-6000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-5600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-7700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-14700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-12500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-7300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-10300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-4800</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z94" s="3" t="s">
         <v>16</v>
       </c>
@@ -7385,8 +7615,11 @@
       <c r="AD94" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7417,8 +7650,9 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7461,8 +7695,8 @@
       <c r="P96" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -7503,8 +7737,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7589,8 +7826,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7675,8 +7915,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7761,77 +8004,80 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-14600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-4400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-11600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-18300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-7300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-3200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-5000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-11900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-3200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-3300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-4800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>17400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-60200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>2400</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>16</v>
       </c>
@@ -7847,77 +8093,80 @@
       <c r="AD100" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>400</v>
+      </c>
+      <c r="E101" s="3">
         <v>2600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-5200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>2800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>2800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>3200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>3200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-800</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>300</v>
-      </c>
-      <c r="V101" s="3">
-        <v>-1100</v>
       </c>
       <c r="W101" s="3">
         <v>-1100</v>
       </c>
       <c r="X101" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="Y101" s="3">
         <v>600</v>
       </c>
-      <c r="Y101" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z101" s="3" t="s">
         <v>16</v>
       </c>
@@ -7933,77 +8182,80 @@
       <c r="AD101" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E102" s="3">
         <v>6000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>10400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>7600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>8900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-89200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>16900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>18300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-13800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>25600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>18200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>11100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>11100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>16200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>3700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>5200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>12000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-61600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>11400</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z102" s="3" t="s">
         <v>16</v>
       </c>
@@ -8017,6 +8269,9 @@
         <v>16</v>
       </c>
       <c r="AD102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AE102" s="3" t="s">
         <v>16</v>
       </c>
     </row>
